--- a/outputs/evaluation/decision/v1/CF_M08/run_1/CF_M08_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M08/run_1/CF_M08_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,37 +471,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
+          <t>Next.js soporta tanto el renderizado de componentes en el lado del cliente (CSR) como el renderizado en el lado del servidor (SSR), utilizando las server actions [...] para comunicar los componentes de cliente con el servidor.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R_28, R_29, C_07</t>
+          <t>R_18, C_02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_03, AU_06, AU_15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>The system must be scalable to handle an increase in the number of users and volume of data.; Ability to increase server resources and maintain performance with a 50% increase in workload.; 12g. Expansion or Growth Requirements</t>
+          <t>The user interface must be intuitive and easy to use for non-technical users.; 11a. Ease of Use Requirements</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>System Service; Next.js; React</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -515,307 +515,57 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6187</v>
+        <v>0.7244</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers an additional structure, features and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>La arquitectura implementada para el desarrollo del sistema del proyecto Revivack es una arquitectura basada en microservicios. La arquitectura de software basada en microservicios es un enfoque de diseño y desarrollo de software donde una aplicación se construye como una colección de servicios pequeños e independientes que se comunican entre sí. En el caso de esta aplicación, dichos servicios se ejecutan en instancias de Amazon EC2 y son gestionados por Docker, que administra la ejecución de los contenedores.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R_18, C_02</t>
+          <t>R_22, R_28, C_04, C_07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_03, AU_06</t>
+          <t>AU_09, P_01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The user interface must be intuitive and easy to use for non-technical users.; 11a. Ease of Use Requirements</t>
+          <t>The system must have an uptime of 99.9% and be able to recover from failures in less than 1 hour.; The system must be scalable to handle an increase in the number of users and volume of data.; 12e. Robustness or Fault Tolerance Requirements; 12g. Expansion or Growth Requirements</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>System Service; Next.js</t>
+          <t>Docker; Microservices</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.7456</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_04</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PostgreSQL provides the relational database for storing application data.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>R_07, R_30, R_31, C_03</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AU_04, AU_07</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>The system must be able to save all images of all products/users in the system.; A company's products/routes/profile can only be editable and accessible by that company.; Verify that only company users can access their products/routes/profile.; 15c. Privacy Requirements</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Data Service; PostgreSQL</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CF_M08_AD11</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.7294</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Docker is a containerization platform used to manage the execution of the application services.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C_06</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>14c. Adaptability Requirements</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Docker</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.6374</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components, which promotes modularity, code reuse, and maintainability.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>R_18, C_02</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>The user interface must be intuitive and easy to use for non-technical users.; 11a. Ease of Use Requirements</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Component-Based</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>CF_M08_AD09</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.7342</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AD_08</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, where a subject maintains a list of observers, allowing them to react appropriately when the subject's state changes.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>C_05</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>14a. Maintenance Requirements</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Observer Pattern</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.6075</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AD_09</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance, used to manage shared resources where having multiple instances could lead to inconsistent states or inefficient resource use.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>C_05</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>14a. Maintenance Requirements</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Singleton Pattern</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.6768</v>
       </c>
     </row>
   </sheetData>
